--- a/public/data/catalogo.xlsx
+++ b/public/data/catalogo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0e5fafb74c2e4150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3896d913a626427c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
       <x:alignment vertical="top"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top"/>
@@ -162,6 +162,14 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -347,67 +355,67 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="60" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="2.690000057220459" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.289999961853027" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="4.980000019073486" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.539999961853027" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.359999656677246" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="4.980000019073486" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="5.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="5.920000076293945" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12.920000076293945" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="8.34000015258789" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="4.980000019073486" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="4.980000019073486" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="7" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>sku</x:v>
       </x:c>
-      <x:c r="B1" s="7" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>nombre</x:v>
       </x:c>
-      <x:c r="C1" s="7" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>descripcion</x:v>
       </x:c>
-      <x:c r="D1" s="7" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>precio</x:v>
       </x:c>
-      <x:c r="E1" s="7" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>precio_oferta</x:v>
       </x:c>
-      <x:c r="F1" s="7" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>categoria</x:v>
       </x:c>
-      <x:c r="G1" s="7" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>subcategoria</x:v>
       </x:c>
-      <x:c r="H1" s="7" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>marca</x:v>
       </x:c>
-      <x:c r="I1" s="7" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>stock</x:v>
       </x:c>
-      <x:c r="J1" s="7" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>estado</x:v>
       </x:c>
-      <x:c r="K1" s="7" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>imagen</x:v>
       </x:c>
-      <x:c r="L1" s="7" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>imagenes_extra</x:v>
       </x:c>
-      <x:c r="M1" s="7" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>destacado</x:v>
       </x:c>
-      <x:c r="N1" s="7" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>nuevo</x:v>
       </x:c>
-      <x:c r="O1" s="7" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>oferta</x:v>
       </x:c>
     </x:row>
@@ -3617,7 +3625,7 @@
         <x:v>Aretes Ala Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C84" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño ala, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D84" s="22" t="n">
         <x:v>67000</x:v>
@@ -3626,7 +3634,9 @@
       <x:c r="F84" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G84" s="16"/>
+      <x:c r="G84" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H84" s="16"/>
       <x:c r="I84" s="24" t="n">
         <x:v>10</x:v>
@@ -3809,10 +3819,10 @@
         <x:v>RR1401</x:v>
       </x:c>
       <x:c r="B89" s="17" t="str">
-        <x:v>Aretes Flor Broche Seguridad Oro Laminado 18K</x:v>
+        <x:v>Aretes Flor Broche de Seguridad Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C89" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño flor broche de seguridad, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D89" s="22" t="n">
         <x:v>91000</x:v>
@@ -3821,7 +3831,9 @@
       <x:c r="F89" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G89" s="16"/>
+      <x:c r="G89" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H89" s="16"/>
       <x:c r="I89" s="24" t="n">
         <x:v>10</x:v>
@@ -5021,7 +5033,7 @@
         <x:v>Aretes Greta Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C120" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño aretes, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D120" s="22" t="n">
         <x:v>87000</x:v>
@@ -5030,7 +5042,9 @@
       <x:c r="F120" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G120" s="16"/>
+      <x:c r="G120" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H120" s="16"/>
       <x:c r="I120" s="24" t="n">
         <x:v>10</x:v>
@@ -11144,7 +11158,7 @@
         <x:v>Aretes Abeja Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C277" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño abeja, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D277" s="22" t="n">
         <x:v>49000</x:v>
@@ -11153,7 +11167,9 @@
       <x:c r="F277" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G277" s="16"/>
+      <x:c r="G277" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H277" s="16"/>
       <x:c r="I277" s="24" t="n">
         <x:v>10</x:v>
@@ -11180,10 +11196,10 @@
         <x:v>RR0817</x:v>
       </x:c>
       <x:c r="B278" s="17" t="str">
-        <x:v>Aretes Ancla Oro Laminado 18K</x:v>
+        <x:v>Aretes Ancla Greta Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C278" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño ancla, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D278" s="22" t="n">
         <x:v>79500</x:v>
@@ -11192,7 +11208,9 @@
       <x:c r="F278" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G278" s="16"/>
+      <x:c r="G278" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H278" s="16"/>
       <x:c r="I278" s="24" t="n">
         <x:v>10</x:v>
@@ -11219,10 +11237,10 @@
         <x:v>RR0672</x:v>
       </x:c>
       <x:c r="B279" s="17" t="str">
-        <x:v>Aretes Ancla Mónaco Oro Laminado 18K</x:v>
+        <x:v>Aretes Ancla Alicia Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C279" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño ancla, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D279" s="22" t="n">
         <x:v>80000</x:v>
@@ -11231,7 +11249,9 @@
       <x:c r="F279" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G279" s="16"/>
+      <x:c r="G279" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H279" s="16"/>
       <x:c r="I279" s="24" t="n">
         <x:v>10</x:v>
@@ -11261,7 +11281,7 @@
         <x:v>Aretes Angelito Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C280" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño angelito, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D280" s="22" t="n">
         <x:v>80000</x:v>
@@ -11270,7 +11290,9 @@
       <x:c r="F280" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G280" s="16"/>
+      <x:c r="G280" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H280" s="16"/>
       <x:c r="I280" s="24" t="n">
         <x:v>10</x:v>
@@ -11453,10 +11475,10 @@
         <x:v>RR1410</x:v>
       </x:c>
       <x:c r="B285" s="17" t="str">
-        <x:v>Aretes Corazón Oro Laminado 18K</x:v>
+        <x:v>Aretes Corazón Greta Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C285" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño corazón, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D285" s="22" t="n">
         <x:v>59000</x:v>
@@ -11465,7 +11487,9 @@
       <x:c r="F285" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G285" s="16"/>
+      <x:c r="G285" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H285" s="16"/>
       <x:c r="I285" s="24" t="n">
         <x:v>10</x:v>
@@ -11492,10 +11516,10 @@
         <x:v>RR1403</x:v>
       </x:c>
       <x:c r="B286" s="17" t="str">
-        <x:v>Aretes Corazón Perla Oro Laminado 18K</x:v>
+        <x:v>Aretes Corazón Alicia Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C286" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño corazón, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D286" s="22" t="n">
         <x:v>37000</x:v>
@@ -11504,7 +11528,9 @@
       <x:c r="F286" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G286" s="16"/>
+      <x:c r="G286" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H286" s="16"/>
       <x:c r="I286" s="24" t="n">
         <x:v>10</x:v>
@@ -11882,10 +11908,10 @@
         <x:v>RR1689</x:v>
       </x:c>
       <x:c r="B296" s="17" t="str">
-        <x:v>Aretes Corazón con Broche Seguridad Oro Laminado 18K</x:v>
+        <x:v>Aretes Corazón con Broche de Seguridad Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C296" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño corazón con broche de seguridad, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D296" s="22" t="n">
         <x:v>71000</x:v>
@@ -11894,7 +11920,9 @@
       <x:c r="F296" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G296" s="16"/>
+      <x:c r="G296" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H296" s="16"/>
       <x:c r="I296" s="24" t="n">
         <x:v>10</x:v>
@@ -12041,7 +12069,7 @@
         <x:v>Aretes Double Free Love Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C300" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño double free love, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D300" s="22" t="n">
         <x:v>111500</x:v>
@@ -12050,7 +12078,9 @@
       <x:c r="F300" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G300" s="16"/>
+      <x:c r="G300" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H300" s="16"/>
       <x:c r="I300" s="24" t="n">
         <x:v>10</x:v>
@@ -12077,10 +12107,10 @@
         <x:v>RR1420</x:v>
       </x:c>
       <x:c r="B301" s="17" t="str">
-        <x:v>Aretes Estrella Oro Laminado 18K</x:v>
+        <x:v>Aretes Estrella Greta Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C301" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño estrella, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D301" s="22" t="n">
         <x:v>57000</x:v>
@@ -12089,7 +12119,9 @@
       <x:c r="F301" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G301" s="16"/>
+      <x:c r="G301" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H301" s="16"/>
       <x:c r="I301" s="24" t="n">
         <x:v>10</x:v>
@@ -12116,10 +12148,10 @@
         <x:v>RR1398</x:v>
       </x:c>
       <x:c r="B302" s="17" t="str">
-        <x:v>Aretes Estrella Aria Oro Laminado 18K</x:v>
+        <x:v>Aretes Estrella Alicia Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C302" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño estrella, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D302" s="22" t="n">
         <x:v>34000</x:v>
@@ -12128,7 +12160,9 @@
       <x:c r="F302" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G302" s="16"/>
+      <x:c r="G302" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H302" s="16"/>
       <x:c r="I302" s="24" t="n">
         <x:v>10</x:v>
@@ -12155,10 +12189,10 @@
         <x:v>RR0811</x:v>
       </x:c>
       <x:c r="B303" s="17" t="str">
-        <x:v>Aretes Estrella Capri Oro Laminado 18K</x:v>
+        <x:v>Aretes Estrella Clara Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C303" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño estrella, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D303" s="22" t="n">
         <x:v>33000</x:v>
@@ -12167,7 +12201,9 @@
       <x:c r="F303" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G303" s="16"/>
+      <x:c r="G303" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H303" s="16"/>
       <x:c r="I303" s="24" t="n">
         <x:v>10</x:v>
@@ -12350,10 +12386,10 @@
         <x:v>RR0653</x:v>
       </x:c>
       <x:c r="B308" s="17" t="str">
-        <x:v>Aretes Flor Circon con Broche de Seguridad Oro Laminado 18K</x:v>
+        <x:v>Aretes Flor Circón con Broche de Seguridad Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C308" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño flor circón con broche de seguridad, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D308" s="22" t="n">
         <x:v>91000</x:v>
@@ -12362,7 +12398,9 @@
       <x:c r="F308" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G308" s="16"/>
+      <x:c r="G308" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H308" s="16"/>
       <x:c r="I308" s="24" t="n">
         <x:v>10</x:v>
@@ -12587,7 +12625,7 @@
         <x:v>Aretes Gucci Medianos Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C314" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño gucci medianos, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D314" s="22" t="n">
         <x:v>73000</x:v>
@@ -12596,7 +12634,9 @@
       <x:c r="F314" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G314" s="16"/>
+      <x:c r="G314" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H314" s="16"/>
       <x:c r="I314" s="24" t="n">
         <x:v>10</x:v>
@@ -12626,7 +12666,7 @@
         <x:v>Aretes Gucci Pequeños Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C315" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño gucci pequeños, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D315" s="22" t="n">
         <x:v>50000</x:v>
@@ -12635,7 +12675,9 @@
       <x:c r="F315" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G315" s="16"/>
+      <x:c r="G315" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H315" s="16"/>
       <x:c r="I315" s="24" t="n">
         <x:v>10</x:v>
@@ -12704,7 +12746,7 @@
         <x:v>Aretes L Byzantine Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C317" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño l byzantine, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D317" s="22" t="n">
         <x:v>83500</x:v>
@@ -12713,7 +12755,9 @@
       <x:c r="F317" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G317" s="16"/>
+      <x:c r="G317" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H317" s="16"/>
       <x:c r="I317" s="24" t="n">
         <x:v>10</x:v>
@@ -13055,7 +13099,7 @@
         <x:v>Aretes Palmeras Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C326" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño palmeras, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D326" s="22" t="n">
         <x:v>67000</x:v>
@@ -13064,7 +13108,9 @@
       <x:c r="F326" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G326" s="16"/>
+      <x:c r="G326" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H326" s="16"/>
       <x:c r="I326" s="24" t="n">
         <x:v>10</x:v>
@@ -13094,7 +13140,7 @@
         <x:v>Aretes Topos Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C327" s="17" t="str">
-        <x:v>Aretes en oro laminado 18K con diseño femenino y versátil, ideales para dar luz al rostro. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Aretes en oro laminado 18K con diseño topos, ideales para iluminar el rostro con un brillo femenino y elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D327" s="22" t="n">
         <x:v>55000</x:v>
@@ -13103,7 +13149,9 @@
       <x:c r="F327" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G327" s="16"/>
+      <x:c r="G327" s="16" t="str">
+        <x:v>Aretes</x:v>
+      </x:c>
       <x:c r="H327" s="16"/>
       <x:c r="I327" s="24" t="n">
         <x:v>10</x:v>
@@ -13364,10 +13412,10 @@
         <x:v>RR1706</x:v>
       </x:c>
       <x:c r="B334" s="17" t="str">
-        <x:v>Argolla Oro Laminado 18K</x:v>
+        <x:v>Argollas Vera Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C334" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D334" s="22" t="n">
         <x:v>58000</x:v>
@@ -13376,7 +13424,9 @@
       <x:c r="F334" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G334" s="16"/>
+      <x:c r="G334" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H334" s="16"/>
       <x:c r="I334" s="24" t="n">
         <x:v>10</x:v>
@@ -13481,10 +13531,10 @@
         <x:v>RR1707</x:v>
       </x:c>
       <x:c r="B337" s="17" t="str">
-        <x:v>Argollas Vera Oro Laminado 18K</x:v>
+        <x:v>Argollas Lunaire Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C337" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D337" s="22" t="n">
         <x:v>78000</x:v>
@@ -13493,7 +13543,9 @@
       <x:c r="F337" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G337" s="16"/>
+      <x:c r="G337" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H337" s="16"/>
       <x:c r="I337" s="24" t="n">
         <x:v>10</x:v>
@@ -13520,10 +13572,10 @@
         <x:v>RR1688</x:v>
       </x:c>
       <x:c r="B338" s="17" t="str">
-        <x:v>Argollas Lunaire Oro Laminado 18K</x:v>
+        <x:v>Argollas Rosa Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C338" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D338" s="22" t="n">
         <x:v>95000</x:v>
@@ -13532,7 +13584,9 @@
       <x:c r="F338" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G338" s="16"/>
+      <x:c r="G338" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H338" s="16"/>
       <x:c r="I338" s="24" t="n">
         <x:v>10</x:v>
@@ -15938,10 +15992,10 @@
         <x:v>RR1450</x:v>
       </x:c>
       <x:c r="B400" s="17" t="str">
-        <x:v>Argollas Rosa Oro Laminado 18K</x:v>
+        <x:v>Argollas Pétalo Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C400" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D400" s="22" t="n">
         <x:v>83000</x:v>
@@ -15950,7 +16004,9 @@
       <x:c r="F400" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G400" s="16"/>
+      <x:c r="G400" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H400" s="16"/>
       <x:c r="I400" s="24" t="n">
         <x:v>10</x:v>
@@ -15977,10 +16033,10 @@
         <x:v>RR1421</x:v>
       </x:c>
       <x:c r="B401" s="17" t="str">
-        <x:v>Argollas Pétalo Oro Laminado 18K</x:v>
+        <x:v>Argollas Selene Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C401" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D401" s="22" t="n">
         <x:v>87000</x:v>
@@ -15989,7 +16045,9 @@
       <x:c r="F401" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G401" s="16"/>
+      <x:c r="G401" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H401" s="16"/>
       <x:c r="I401" s="24" t="n">
         <x:v>10</x:v>
@@ -16016,10 +16074,10 @@
         <x:v>RR1412</x:v>
       </x:c>
       <x:c r="B402" s="17" t="str">
-        <x:v>Argollas Selene Oro Laminado 18K</x:v>
+        <x:v>Argollas Mía Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C402" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D402" s="22" t="n">
         <x:v>70000</x:v>
@@ -16028,7 +16086,9 @@
       <x:c r="F402" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G402" s="16"/>
+      <x:c r="G402" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H402" s="16"/>
       <x:c r="I402" s="24" t="n">
         <x:v>10</x:v>
@@ -16055,10 +16115,10 @@
         <x:v>RR1395</x:v>
       </x:c>
       <x:c r="B403" s="17" t="str">
-        <x:v>Argollas Mía Oro Laminado 18K</x:v>
+        <x:v>Argollas Elsa Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C403" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D403" s="22" t="n">
         <x:v>62000</x:v>
@@ -16067,7 +16127,9 @@
       <x:c r="F403" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G403" s="16"/>
+      <x:c r="G403" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H403" s="16"/>
       <x:c r="I403" s="24" t="n">
         <x:v>10</x:v>
@@ -17810,10 +17872,10 @@
         <x:v>RR0818</x:v>
       </x:c>
       <x:c r="B448" s="17" t="str">
-        <x:v>Argollas Delicado Oro Laminado 18K</x:v>
+        <x:v>Argollas Nora Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C448" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D448" s="22" t="n">
         <x:v>92500</x:v>
@@ -17822,7 +17884,9 @@
       <x:c r="F448" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G448" s="16"/>
+      <x:c r="G448" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H448" s="16"/>
       <x:c r="I448" s="24" t="n">
         <x:v>10</x:v>
@@ -17849,10 +17913,10 @@
         <x:v>RR0815</x:v>
       </x:c>
       <x:c r="B449" s="17" t="str">
-        <x:v>Argollas Elsa Oro Laminado 18K</x:v>
+        <x:v>Argollas Solé Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C449" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D449" s="22" t="n">
         <x:v>92000</x:v>
@@ -17861,7 +17925,9 @@
       <x:c r="F449" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G449" s="16"/>
+      <x:c r="G449" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H449" s="16"/>
       <x:c r="I449" s="24" t="n">
         <x:v>10</x:v>
@@ -17888,10 +17954,10 @@
         <x:v>RR0809</x:v>
       </x:c>
       <x:c r="B450" s="17" t="str">
-        <x:v>Argollas Rosa Oro Laminado 18K Coral</x:v>
+        <x:v>Argollas Celeste Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C450" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D450" s="22" t="n">
         <x:v>43000</x:v>
@@ -17900,7 +17966,9 @@
       <x:c r="F450" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G450" s="16"/>
+      <x:c r="G450" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H450" s="16"/>
       <x:c r="I450" s="24" t="n">
         <x:v>10</x:v>
@@ -17927,10 +17995,10 @@
         <x:v>RR0652</x:v>
       </x:c>
       <x:c r="B451" s="17" t="str">
-        <x:v>Argollas Lía Oro Laminado 18K</x:v>
+        <x:v>Argollas Lucía Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C451" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño argollas, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D451" s="22" t="n">
         <x:v>78000</x:v>
@@ -17939,7 +18007,9 @@
       <x:c r="F451" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G451" s="16"/>
+      <x:c r="G451" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H451" s="16"/>
       <x:c r="I451" s="24" t="n">
         <x:v>10</x:v>
@@ -19490,7 +19560,7 @@
         <x:v>Argollas Cruz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C491" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño cruz, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D491" s="22" t="n">
         <x:v>85000</x:v>
@@ -19499,7 +19569,9 @@
       <x:c r="F491" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G491" s="16"/>
+      <x:c r="G491" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H491" s="16"/>
       <x:c r="I491" s="24" t="n">
         <x:v>10</x:v>
@@ -19529,7 +19601,7 @@
         <x:v>Argollas Niña Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C492" s="17" t="str">
-        <x:v>Argollas en oro laminado 18K de estilo versátil, fáciles de combinar para uso diario. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Argollas en oro laminado 18K con diseño niña, perfectas para sumar brillo y presencia sin perder delicadeza. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D492" s="22" t="n">
         <x:v>47000</x:v>
@@ -19538,7 +19610,9 @@
       <x:c r="F492" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G492" s="16"/>
+      <x:c r="G492" s="16" t="str">
+        <x:v>Argollas</x:v>
+      </x:c>
       <x:c r="H492" s="16"/>
       <x:c r="I492" s="24" t="n">
         <x:v>10</x:v>
@@ -20579,10 +20653,10 @@
         <x:v>RR1394</x:v>
       </x:c>
       <x:c r="B519" s="17" t="str">
-        <x:v>Cadena Nerea Oro Laminado 18K</x:v>
+        <x:v>Cadena Siena Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C519" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K de estilo clásico y versátil, ideal para usar sola o combinar con dijes. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D519" s="22" t="n">
         <x:v>318000</x:v>
@@ -20591,7 +20665,9 @@
       <x:c r="F519" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G519" s="16"/>
+      <x:c r="G519" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H519" s="16"/>
       <x:c r="I519" s="24" t="n">
         <x:v>10</x:v>
@@ -20618,10 +20694,10 @@
         <x:v>RR1383</x:v>
       </x:c>
       <x:c r="B520" s="17" t="str">
-        <x:v>Cadena Bianca Oro Laminado 18K</x:v>
+        <x:v>Cadena Dalia Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C520" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K de estilo clásico y versátil, ideal para usar sola o combinar con dijes. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D520" s="22" t="n">
         <x:v>255000</x:v>
@@ -20630,7 +20706,9 @@
       <x:c r="F520" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G520" s="16"/>
+      <x:c r="G520" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H520" s="16"/>
       <x:c r="I520" s="24" t="n">
         <x:v>10</x:v>
@@ -20657,10 +20735,10 @@
         <x:v>RR1382</x:v>
       </x:c>
       <x:c r="B521" s="17" t="str">
-        <x:v>Cadena Dalia Oro Laminado 18K</x:v>
+        <x:v>Cadena Lía Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C521" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K de estilo clásico y versátil, ideal para usar sola o combinar con dijes. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D521" s="22" t="n">
         <x:v>302000</x:v>
@@ -20669,7 +20747,9 @@
       <x:c r="F521" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G521" s="16"/>
+      <x:c r="G521" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H521" s="16"/>
       <x:c r="I521" s="24" t="n">
         <x:v>10</x:v>
@@ -20696,10 +20776,10 @@
         <x:v>RR1381</x:v>
       </x:c>
       <x:c r="B522" s="17" t="str">
-        <x:v>Cadena Cereza Oro Laminado 18K</x:v>
+        <x:v>Cadena Celine Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C522" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K de estilo clásico y versátil, ideal para usar sola o combinar con dijes. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D522" s="22" t="n">
         <x:v>176000</x:v>
@@ -20708,7 +20788,9 @@
       <x:c r="F522" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G522" s="16"/>
+      <x:c r="G522" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H522" s="16"/>
       <x:c r="I522" s="24" t="n">
         <x:v>10</x:v>
@@ -20972,7 +21054,7 @@
         <x:v>Cadena 3x1 Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C529" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo 3x1, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D529" s="22" t="n">
         <x:v>164000</x:v>
@@ -20981,7 +21063,9 @@
       <x:c r="F529" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G529" s="16"/>
+      <x:c r="G529" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H529" s="16"/>
       <x:c r="I529" s="24" t="n">
         <x:v>10</x:v>
@@ -21281,10 +21365,10 @@
         <x:v>RR1386</x:v>
       </x:c>
       <x:c r="B537" s="17" t="str">
-        <x:v>Cadena Balin Oro Laminado 18K</x:v>
+        <x:v>Cadena Balín Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C537" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo balín, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D537" s="22" t="n">
         <x:v>398000</x:v>
@@ -21293,7 +21377,9 @@
       <x:c r="F537" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G537" s="16"/>
+      <x:c r="G537" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H537" s="16"/>
       <x:c r="I537" s="24" t="n">
         <x:v>10</x:v>
@@ -21320,10 +21406,10 @@
         <x:v>RR0345</x:v>
       </x:c>
       <x:c r="B538" s="17" t="str">
-        <x:v>Cadena Caracol Gruesa 45 Cms Oro Laminado 18K</x:v>
+        <x:v>Cadena Caracol Gruesa 45 cm Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C538" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo caracol gruesa 45 cm, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D538" s="22" t="n">
         <x:v>241000</x:v>
@@ -21332,7 +21418,9 @@
       <x:c r="F538" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G538" s="16"/>
+      <x:c r="G538" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H538" s="16"/>
       <x:c r="I538" s="24" t="n">
         <x:v>10</x:v>
@@ -21362,7 +21450,7 @@
         <x:v>Cadena Cubanita Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C539" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo cubanita, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D539" s="22" t="n">
         <x:v>285000</x:v>
@@ -21371,7 +21459,9 @@
       <x:c r="F539" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G539" s="16"/>
+      <x:c r="G539" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H539" s="16"/>
       <x:c r="I539" s="24" t="n">
         <x:v>10</x:v>
@@ -21401,7 +21491,7 @@
         <x:v>Cadena Escalera Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C540" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo escalera, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D540" s="22" t="n">
         <x:v>252000</x:v>
@@ -21410,7 +21500,9 @@
       <x:c r="F540" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G540" s="16"/>
+      <x:c r="G540" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H540" s="16"/>
       <x:c r="I540" s="24" t="n">
         <x:v>10</x:v>
@@ -21515,10 +21607,10 @@
         <x:v>RR0320</x:v>
       </x:c>
       <x:c r="B543" s="17" t="str">
-        <x:v>Cadena Lazo Diamantado 1.7 Mm 45 Cms Oro Laminado 18K</x:v>
+        <x:v>Cadena Lazo Diamantado 1.7 mm 45 cm Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C543" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo lazo diamantado 1.7 mm 45 cm, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D543" s="22" t="n">
         <x:v>200000</x:v>
@@ -21527,7 +21619,9 @@
       <x:c r="F543" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G543" s="16"/>
+      <x:c r="G543" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H543" s="16"/>
       <x:c r="I543" s="24" t="n">
         <x:v>10</x:v>
@@ -21554,10 +21648,10 @@
         <x:v>RR0322</x:v>
       </x:c>
       <x:c r="B544" s="17" t="str">
-        <x:v>Cadena Serpiente 4 Mm 65 Cms Oro Laminado 18K</x:v>
+        <x:v>Cadena Serpiente 4 mm 65 cm Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C544" s="17" t="str">
-        <x:v>Cadena en oro laminado 18K de estilo limpio, ideal para usar sola o con dije. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Cadena en oro laminado 18K estilo serpiente 4 mm 65 cm, versátil para usar sola o combinar con tus dijes favoritos. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D544" s="22" t="n">
         <x:v>611500</x:v>
@@ -21566,7 +21660,9 @@
       <x:c r="F544" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G544" s="16"/>
+      <x:c r="G544" s="16" t="str">
+        <x:v>Cadenas</x:v>
+      </x:c>
       <x:c r="H544" s="16"/>
       <x:c r="I544" s="24" t="n">
         <x:v>10</x:v>
@@ -21593,10 +21689,10 @@
         <x:v>RR0388</x:v>
       </x:c>
       <x:c r="B545" s="17" t="str">
-        <x:v>Candonga Badge 2.8 Cm Oro Laminado 18K</x:v>
+        <x:v>Candonga Badge 2.8 cm Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C545" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Candongas en oro laminado 18K con diseño badge 2.8 cm, una opción clásica y luminosa para completar tu estilo. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D545" s="22" t="n">
         <x:v>93000</x:v>
@@ -21605,7 +21701,9 @@
       <x:c r="F545" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G545" s="16"/>
+      <x:c r="G545" s="16" t="str">
+        <x:v>Candongas</x:v>
+      </x:c>
       <x:c r="H545" s="16"/>
       <x:c r="I545" s="24" t="n">
         <x:v>10</x:v>
@@ -21632,10 +21730,10 @@
         <x:v>RR0389</x:v>
       </x:c>
       <x:c r="B546" s="17" t="str">
-        <x:v>Candonga Lisa Plana 3 Cm Oro Laminado 18K</x:v>
+        <x:v>Candonga Lisa Plana 3 cm Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C546" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Candongas en oro laminado 18K con diseño lisa plana 3 cm, una opción clásica y luminosa para completar tu estilo. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D546" s="22" t="n">
         <x:v>70000</x:v>
@@ -21644,7 +21742,9 @@
       <x:c r="F546" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G546" s="16"/>
+      <x:c r="G546" s="16" t="str">
+        <x:v>Candongas</x:v>
+      </x:c>
       <x:c r="H546" s="16"/>
       <x:c r="I546" s="24" t="n">
         <x:v>10</x:v>
@@ -21674,7 +21774,7 @@
         <x:v>Candonga Rainbow Star Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C547" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Candongas en oro laminado 18K con diseño rainbow star, una opción clásica y luminosa para completar tu estilo. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D547" s="22" t="n">
         <x:v>102500</x:v>
@@ -21683,7 +21783,9 @@
       <x:c r="F547" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G547" s="16"/>
+      <x:c r="G547" s="16" t="str">
+        <x:v>Candongas</x:v>
+      </x:c>
       <x:c r="H547" s="16"/>
       <x:c r="I547" s="24" t="n">
         <x:v>10</x:v>
@@ -21710,10 +21812,10 @@
         <x:v>RR0385</x:v>
       </x:c>
       <x:c r="B548" s="17" t="str">
-        <x:v>Candonga Steel 1.5 Cm Oro Laminado 18K</x:v>
+        <x:v>Candonga Steel 1.5 cm Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C548" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Candongas en oro laminado 18K con diseño steel 1.5 cm, una opción clásica y luminosa para completar tu estilo. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D548" s="22" t="n">
         <x:v>83500</x:v>
@@ -21722,7 +21824,9 @@
       <x:c r="F548" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G548" s="16"/>
+      <x:c r="G548" s="16" t="str">
+        <x:v>Candongas</x:v>
+      </x:c>
       <x:c r="H548" s="16"/>
       <x:c r="I548" s="24" t="n">
         <x:v>10</x:v>
@@ -22220,7 +22324,7 @@
         <x:v>Dije Arcángel San Gabriel Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C561" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño arcángel san gabriel, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D561" s="22" t="n">
         <x:v>106000</x:v>
@@ -22229,7 +22333,9 @@
       <x:c r="F561" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G561" s="16"/>
+      <x:c r="G561" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H561" s="16"/>
       <x:c r="I561" s="24" t="n">
         <x:v>10</x:v>
@@ -22256,10 +22362,10 @@
         <x:v>RR0667</x:v>
       </x:c>
       <x:c r="B562" s="17" t="str">
-        <x:v>Dije Avion Oro Laminado 18K</x:v>
+        <x:v>Dije Avión Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C562" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño avión, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D562" s="22" t="n">
         <x:v>66500</x:v>
@@ -22268,7 +22374,9 @@
       <x:c r="F562" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G562" s="16"/>
+      <x:c r="G562" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H562" s="16"/>
       <x:c r="I562" s="24" t="n">
         <x:v>10</x:v>
@@ -22337,7 +22445,7 @@
         <x:v>Dije Boy Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C564" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño boy, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D564" s="22" t="n">
         <x:v>47000</x:v>
@@ -22346,7 +22454,9 @@
       <x:c r="F564" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G564" s="16"/>
+      <x:c r="G564" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H564" s="16"/>
       <x:c r="I564" s="24" t="n">
         <x:v>10</x:v>
@@ -22529,10 +22639,10 @@
         <x:v>RR1708</x:v>
       </x:c>
       <x:c r="B569" s="17" t="str">
-        <x:v>Dije Corazón Oro Laminado 18K</x:v>
+        <x:v>Dije Corazón Luz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C569" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño corazón, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D569" s="22" t="n">
         <x:v>21000</x:v>
@@ -22541,7 +22651,9 @@
       <x:c r="F569" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G569" s="16"/>
+      <x:c r="G569" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H569" s="16"/>
       <x:c r="I569" s="24" t="n">
         <x:v>10</x:v>
@@ -22607,10 +22719,10 @@
         <x:v>RR1406</x:v>
       </x:c>
       <x:c r="B571" s="17" t="str">
-        <x:v>Dije Corazón Eloísa Oro Laminado 18K</x:v>
+        <x:v>Dije Corazón Amelie Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C571" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño corazón, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D571" s="22" t="n">
         <x:v>48000</x:v>
@@ -22619,7 +22731,9 @@
       <x:c r="F571" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G571" s="16"/>
+      <x:c r="G571" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H571" s="16"/>
       <x:c r="I571" s="24" t="n">
         <x:v>10</x:v>
@@ -22763,10 +22877,10 @@
         <x:v>RR0812</x:v>
       </x:c>
       <x:c r="B575" s="17" t="str">
-        <x:v>Dije Corazón Celeste Oro Laminado 18K</x:v>
+        <x:v>Dije Corazón Serena Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C575" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño corazón, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D575" s="22" t="n">
         <x:v>50500</x:v>
@@ -22775,7 +22889,9 @@
       <x:c r="F575" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G575" s="16"/>
+      <x:c r="G575" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H575" s="16"/>
       <x:c r="I575" s="24" t="n">
         <x:v>10</x:v>
@@ -23078,7 +23194,7 @@
         <x:v>Dije Corazón+cruz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C583" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño corazón+cruz, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D583" s="22" t="n">
         <x:v>62500</x:v>
@@ -23087,7 +23203,9 @@
       <x:c r="F583" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G583" s="16"/>
+      <x:c r="G583" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H583" s="16"/>
       <x:c r="I583" s="24" t="n">
         <x:v>10</x:v>
@@ -23117,7 +23235,7 @@
         <x:v>Dije Corchea Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C584" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño corchea, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D584" s="22" t="n">
         <x:v>25000</x:v>
@@ -23126,7 +23244,9 @@
       <x:c r="F584" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G584" s="16"/>
+      <x:c r="G584" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H584" s="16"/>
       <x:c r="I584" s="24" t="n">
         <x:v>10</x:v>
@@ -23195,7 +23315,7 @@
         <x:v>Dije Cristo Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C586" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño cristo, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D586" s="22" t="n">
         <x:v>21000</x:v>
@@ -23204,7 +23324,9 @@
       <x:c r="F586" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G586" s="16"/>
+      <x:c r="G586" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H586" s="16"/>
       <x:c r="I586" s="24" t="n">
         <x:v>1</x:v>
@@ -23273,7 +23395,7 @@
         <x:v>Dije Cristo Cruz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C588" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño cristo cruz, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D588" s="22" t="n">
         <x:v>42000</x:v>
@@ -23282,7 +23404,9 @@
       <x:c r="F588" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G588" s="16"/>
+      <x:c r="G588" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H588" s="16"/>
       <x:c r="I588" s="24" t="n">
         <x:v>10</x:v>
@@ -23309,10 +23433,10 @@
         <x:v>RR1423</x:v>
       </x:c>
       <x:c r="B589" s="17" t="str">
-        <x:v>Dije Cruz Oro Laminado 18K</x:v>
+        <x:v>Dije Cruz Luz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C589" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño cruz, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D589" s="22" t="n">
         <x:v>32000</x:v>
@@ -23321,7 +23445,9 @@
       <x:c r="F589" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G589" s="16"/>
+      <x:c r="G589" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H589" s="16"/>
       <x:c r="I589" s="24" t="n">
         <x:v>10</x:v>
@@ -23348,10 +23474,10 @@
         <x:v>RR1416</x:v>
       </x:c>
       <x:c r="B590" s="17" t="str">
-        <x:v>Dije Cruz Musa Oro Laminado 18K</x:v>
+        <x:v>Dije Cruz Amelie Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C590" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño cruz, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D590" s="22" t="n">
         <x:v>21000</x:v>
@@ -23360,7 +23486,9 @@
       <x:c r="F590" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G590" s="16"/>
+      <x:c r="G590" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H590" s="16"/>
       <x:c r="I590" s="24" t="n">
         <x:v>10</x:v>
@@ -23546,7 +23674,7 @@
         <x:v>Dije Cruz Cristo Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C595" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño cruz cristo, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D595" s="22" t="n">
         <x:v>80000</x:v>
@@ -23555,7 +23683,9 @@
       <x:c r="F595" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G595" s="16"/>
+      <x:c r="G595" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H595" s="16"/>
       <x:c r="I595" s="24" t="n">
         <x:v>10</x:v>
@@ -23585,7 +23715,7 @@
         <x:v>Dije Cruz Spitze Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C596" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño cruz spitze, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D596" s="22" t="n">
         <x:v>112000</x:v>
@@ -23594,7 +23724,9 @@
       <x:c r="F596" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G596" s="16"/>
+      <x:c r="G596" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H596" s="16"/>
       <x:c r="I596" s="24" t="n">
         <x:v>10</x:v>
@@ -23624,7 +23756,7 @@
         <x:v>Dije Dios Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C597" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño dios, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D597" s="22" t="n">
         <x:v>66500</x:v>
@@ -23633,7 +23765,9 @@
       <x:c r="F597" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G597" s="16"/>
+      <x:c r="G597" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H597" s="16"/>
       <x:c r="I597" s="24" t="n">
         <x:v>10</x:v>
@@ -23819,7 +23953,7 @@
         <x:v>Dije Fe Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C602" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño fe, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D602" s="22" t="n">
         <x:v>56000</x:v>
@@ -23828,7 +23962,9 @@
       <x:c r="F602" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G602" s="16"/>
+      <x:c r="G602" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H602" s="16"/>
       <x:c r="I602" s="24" t="n">
         <x:v>10</x:v>
@@ -23936,7 +24072,7 @@
         <x:v>Dije Flor Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C605" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño flor, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D605" s="22" t="n">
         <x:v>62000</x:v>
@@ -23945,7 +24081,9 @@
       <x:c r="F605" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G605" s="16"/>
+      <x:c r="G605" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H605" s="16"/>
       <x:c r="I605" s="24" t="n">
         <x:v>10</x:v>
@@ -24053,7 +24191,7 @@
         <x:v>Dije Girl Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C608" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño girl, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D608" s="22" t="n">
         <x:v>47000</x:v>
@@ -24062,7 +24200,9 @@
       <x:c r="F608" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G608" s="16"/>
+      <x:c r="G608" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H608" s="16"/>
       <x:c r="I608" s="24" t="n">
         <x:v>10</x:v>
@@ -24131,7 +24271,7 @@
         <x:v>Dije Huella Perro Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C610" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño huella perro, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D610" s="22" t="n">
         <x:v>22000</x:v>
@@ -24140,7 +24280,9 @@
       <x:c r="F610" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G610" s="16"/>
+      <x:c r="G610" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H610" s="16"/>
       <x:c r="I610" s="24" t="n">
         <x:v>10</x:v>
@@ -24170,7 +24312,7 @@
         <x:v>Dije Letra C Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C611" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra c, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D611" s="22" t="n">
         <x:v>39000</x:v>
@@ -24179,7 +24321,9 @@
       <x:c r="F611" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G611" s="16"/>
+      <x:c r="G611" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H611" s="16"/>
       <x:c r="I611" s="24" t="n">
         <x:v>10</x:v>
@@ -24209,7 +24353,7 @@
         <x:v>Dije Letra D Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C612" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra d, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D612" s="22" t="n">
         <x:v>39000</x:v>
@@ -24218,7 +24362,9 @@
       <x:c r="F612" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G612" s="16"/>
+      <x:c r="G612" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H612" s="16"/>
       <x:c r="I612" s="24" t="n">
         <x:v>10</x:v>
@@ -24248,7 +24394,7 @@
         <x:v>Dije Letra E Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C613" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra e, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D613" s="22" t="n">
         <x:v>39000</x:v>
@@ -24257,7 +24403,9 @@
       <x:c r="F613" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G613" s="16"/>
+      <x:c r="G613" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H613" s="16"/>
       <x:c r="I613" s="24" t="n">
         <x:v>10</x:v>
@@ -24287,7 +24435,7 @@
         <x:v>Dije Letra F Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C614" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra f, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D614" s="22" t="n">
         <x:v>54000</x:v>
@@ -24296,7 +24444,9 @@
       <x:c r="F614" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G614" s="16"/>
+      <x:c r="G614" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H614" s="16"/>
       <x:c r="I614" s="24" t="n">
         <x:v>10</x:v>
@@ -24326,7 +24476,7 @@
         <x:v>Dije Letra I Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C615" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra i, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D615" s="22" t="n">
         <x:v>54000</x:v>
@@ -24335,7 +24485,9 @@
       <x:c r="F615" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G615" s="16"/>
+      <x:c r="G615" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H615" s="16"/>
       <x:c r="I615" s="24" t="n">
         <x:v>10</x:v>
@@ -24365,7 +24517,7 @@
         <x:v>Dije Letra O Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C616" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra o, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D616" s="22" t="n">
         <x:v>39000</x:v>
@@ -24374,7 +24526,9 @@
       <x:c r="F616" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G616" s="16"/>
+      <x:c r="G616" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H616" s="16"/>
       <x:c r="I616" s="24" t="n">
         <x:v>10</x:v>
@@ -24401,10 +24555,10 @@
         <x:v>RR1704</x:v>
       </x:c>
       <x:c r="B617" s="17" t="str">
-        <x:v>Dije Letra P Oro Laminado 18K</x:v>
+        <x:v>Dije Letra P Luz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C617" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra p, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D617" s="22" t="n">
         <x:v>30000</x:v>
@@ -24413,7 +24567,9 @@
       <x:c r="F617" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G617" s="16"/>
+      <x:c r="G617" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H617" s="16"/>
       <x:c r="I617" s="24" t="n">
         <x:v>1</x:v>
@@ -24440,10 +24596,10 @@
         <x:v>RR0223</x:v>
       </x:c>
       <x:c r="B618" s="17" t="str">
-        <x:v>Dije Letra P Alba Oro Laminado 18K</x:v>
+        <x:v>Dije Letra P Amelie Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C618" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra p, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D618" s="22" t="n">
         <x:v>39000</x:v>
@@ -24452,7 +24608,9 @@
       <x:c r="F618" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G618" s="16"/>
+      <x:c r="G618" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H618" s="16"/>
       <x:c r="I618" s="24" t="n">
         <x:v>10</x:v>
@@ -24482,7 +24640,7 @@
         <x:v>Dije Letra R Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C619" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra r, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D619" s="22" t="n">
         <x:v>54000</x:v>
@@ -24491,7 +24649,9 @@
       <x:c r="F619" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G619" s="16"/>
+      <x:c r="G619" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H619" s="16"/>
       <x:c r="I619" s="24" t="n">
         <x:v>10</x:v>
@@ -24521,7 +24681,7 @@
         <x:v>Dije Letra T Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C620" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra t, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D620" s="22" t="n">
         <x:v>39000</x:v>
@@ -24530,7 +24690,9 @@
       <x:c r="F620" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G620" s="16"/>
+      <x:c r="G620" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H620" s="16"/>
       <x:c r="I620" s="24" t="n">
         <x:v>10</x:v>
@@ -24560,7 +24722,7 @@
         <x:v>Dije Letra V Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C621" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra v, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D621" s="22" t="n">
         <x:v>54000</x:v>
@@ -24569,7 +24731,9 @@
       <x:c r="F621" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G621" s="16"/>
+      <x:c r="G621" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H621" s="16"/>
       <x:c r="I621" s="24" t="n">
         <x:v>10</x:v>
@@ -24599,7 +24763,7 @@
         <x:v>Dije Letra y Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C622" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño letra y, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D622" s="22" t="n">
         <x:v>39000</x:v>
@@ -24608,7 +24772,9 @@
       <x:c r="F622" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G622" s="16"/>
+      <x:c r="G622" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H622" s="16"/>
       <x:c r="I622" s="24" t="n">
         <x:v>10</x:v>
@@ -24794,7 +24960,7 @@
         <x:v>Dije Nota Musical Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C627" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño nota musical, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D627" s="22" t="n">
         <x:v>32000</x:v>
@@ -24803,7 +24969,9 @@
       <x:c r="F627" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G627" s="16"/>
+      <x:c r="G627" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H627" s="16"/>
       <x:c r="I627" s="24" t="n">
         <x:v>10</x:v>
@@ -24833,7 +25001,7 @@
         <x:v>Dije Placa Cruz Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C628" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño placa cruz, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D628" s="22" t="n">
         <x:v>33000</x:v>
@@ -24842,7 +25010,9 @@
       <x:c r="F628" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G628" s="16"/>
+      <x:c r="G628" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H628" s="16"/>
       <x:c r="I628" s="24" t="n">
         <x:v>10</x:v>
@@ -24872,7 +25042,7 @@
         <x:v>Dije Placa Padre Nuestro Labrado Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C629" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño placa padre nuestro labrado, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D629" s="22" t="n">
         <x:v>44000</x:v>
@@ -24881,7 +25051,9 @@
       <x:c r="F629" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G629" s="16"/>
+      <x:c r="G629" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H629" s="16"/>
       <x:c r="I629" s="24" t="n">
         <x:v>10</x:v>
@@ -24911,7 +25083,7 @@
         <x:v>Dije Rolex Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C630" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño rolex, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D630" s="22" t="n">
         <x:v>55000</x:v>
@@ -24920,7 +25092,9 @@
       <x:c r="F630" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G630" s="16"/>
+      <x:c r="G630" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H630" s="16"/>
       <x:c r="I630" s="24" t="n">
         <x:v>10</x:v>
@@ -25028,7 +25202,7 @@
         <x:v>Dije San Benito Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C633" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño san benito, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D633" s="22" t="n">
         <x:v>30000</x:v>
@@ -25037,7 +25211,9 @@
       <x:c r="F633" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G633" s="16"/>
+      <x:c r="G633" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H633" s="16"/>
       <x:c r="I633" s="24" t="n">
         <x:v>10</x:v>
@@ -25181,10 +25357,10 @@
         <x:v>RR1417</x:v>
       </x:c>
       <x:c r="B637" s="17" t="str">
-        <x:v>Dije Trebol Oro Laminado 18K</x:v>
+        <x:v>Dije Trébol Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C637" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño trébol, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D637" s="22" t="n">
         <x:v>59000</x:v>
@@ -25193,7 +25369,9 @@
       <x:c r="F637" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G637" s="16"/>
+      <x:c r="G637" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H637" s="16"/>
       <x:c r="I637" s="24" t="n">
         <x:v>10</x:v>
@@ -25379,7 +25557,7 @@
         <x:v>Dije Virgen Guadalupe Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C642" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño virgen guadalupe, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D642" s="22" t="n">
         <x:v>30000</x:v>
@@ -25388,7 +25566,9 @@
       <x:c r="F642" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G642" s="16"/>
+      <x:c r="G642" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H642" s="16"/>
       <x:c r="I642" s="24" t="n">
         <x:v>10</x:v>
@@ -25418,7 +25598,7 @@
         <x:v>Dije Virgen Niña Cristal Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C643" s="17" t="str">
-        <x:v>Dije en oro laminado 18K para llevar un detalle especial con acabado delicado. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Dije en oro laminado 18K con diseño virgen niña cristal, ideal para personalizar tu cadena con un detalle simbólico y delicado. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D643" s="22" t="n">
         <x:v>65500</x:v>
@@ -25427,7 +25607,9 @@
       <x:c r="F643" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G643" s="16"/>
+      <x:c r="G643" s="16" t="str">
+        <x:v>Dijes</x:v>
+      </x:c>
       <x:c r="H643" s="16"/>
       <x:c r="I643" s="24" t="n">
         <x:v>10</x:v>
@@ -26624,10 +26806,10 @@
         <x:v>RR1709</x:v>
       </x:c>
       <x:c r="B674" s="17" t="str">
-        <x:v>Gargantilla Dalia Oro Laminado 18K</x:v>
+        <x:v>Gargantilla Amelie Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C674" s="17" t="str">
-        <x:v>Gargantilla en oro laminado 18K con presencia delicada y femenina. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Gargantilla en oro laminado 18K de caída delicada, ideal para iluminar el cuello con un detalle elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D674" s="22" t="n">
         <x:v>119000</x:v>
@@ -26636,7 +26818,9 @@
       <x:c r="F674" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G674" s="16"/>
+      <x:c r="G674" s="16" t="str">
+        <x:v>Gargantillas</x:v>
+      </x:c>
       <x:c r="H674" s="16"/>
       <x:c r="I674" s="24" t="n">
         <x:v>10</x:v>
@@ -26663,10 +26847,10 @@
         <x:v>RR1703</x:v>
       </x:c>
       <x:c r="B675" s="17" t="str">
-        <x:v>Gargantilla Dorado Oro Laminado 18K</x:v>
+        <x:v>Gargantilla Celeste Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C675" s="17" t="str">
-        <x:v>Gargantilla en oro laminado 18K con presencia delicada y femenina. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Gargantilla en oro laminado 18K de caída delicada, ideal para iluminar el cuello con un detalle elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D675" s="22" t="n">
         <x:v>142000</x:v>
@@ -26675,7 +26859,9 @@
       <x:c r="F675" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G675" s="16"/>
+      <x:c r="G675" s="16" t="str">
+        <x:v>Gargantillas</x:v>
+      </x:c>
       <x:c r="H675" s="16"/>
       <x:c r="I675" s="24" t="n">
         <x:v>10</x:v>
@@ -26702,10 +26888,10 @@
         <x:v>RR1702</x:v>
       </x:c>
       <x:c r="B676" s="17" t="str">
-        <x:v>Gargantilla Pétalo Oro Laminado 18K</x:v>
+        <x:v>Gargantilla Olivia Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C676" s="17" t="str">
-        <x:v>Gargantilla en oro laminado 18K con presencia delicada y femenina. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Gargantilla en oro laminado 18K de caída delicada, ideal para iluminar el cuello con un detalle elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D676" s="22" t="n">
         <x:v>121000</x:v>
@@ -26714,7 +26900,9 @@
       <x:c r="F676" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G676" s="16"/>
+      <x:c r="G676" s="16" t="str">
+        <x:v>Gargantillas</x:v>
+      </x:c>
       <x:c r="H676" s="16"/>
       <x:c r="I676" s="24" t="n">
         <x:v>10</x:v>
@@ -27287,10 +27475,10 @@
         <x:v>RR1418</x:v>
       </x:c>
       <x:c r="B691" s="17" t="str">
-        <x:v>Gargantilla Isadora Oro Laminado 18K</x:v>
+        <x:v>Gargantilla Nacar Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C691" s="17" t="str">
-        <x:v>Gargantilla en oro laminado 18K con presencia delicada y femenina. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Gargantilla en oro laminado 18K de caída delicada, ideal para iluminar el cuello con un detalle elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D691" s="22" t="n">
         <x:v>154000</x:v>
@@ -27299,7 +27487,9 @@
       <x:c r="F691" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G691" s="16"/>
+      <x:c r="G691" s="16" t="str">
+        <x:v>Gargantillas</x:v>
+      </x:c>
       <x:c r="H691" s="16"/>
       <x:c r="I691" s="24" t="n">
         <x:v>10</x:v>
@@ -27326,10 +27516,10 @@
         <x:v>RR1415</x:v>
       </x:c>
       <x:c r="B692" s="17" t="str">
-        <x:v>Gargantilla Aurora Oro Laminado 18K</x:v>
+        <x:v>Gargantilla Elena Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C692" s="17" t="str">
-        <x:v>Gargantilla en oro laminado 18K con presencia delicada y femenina. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Gargantilla en oro laminado 18K de caída delicada, ideal para iluminar el cuello con un detalle elegante. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D692" s="22" t="n">
         <x:v>187000</x:v>
@@ -27338,7 +27528,9 @@
       <x:c r="F692" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G692" s="16"/>
+      <x:c r="G692" s="16" t="str">
+        <x:v>Gargantillas</x:v>
+      </x:c>
       <x:c r="H692" s="16"/>
       <x:c r="I692" s="24" t="n">
         <x:v>10</x:v>
@@ -29513,7 +29705,7 @@
         <x:v>Pulsera Tejido Plano Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C748" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo tejido plano, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D748" s="22" t="n">
         <x:v>119000</x:v>
@@ -29522,7 +29714,9 @@
       <x:c r="F748" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G748" s="16"/>
+      <x:c r="G748" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H748" s="16"/>
       <x:c r="I748" s="24" t="n">
         <x:v>10</x:v>
@@ -29588,10 +29782,10 @@
         <x:v>RR1397</x:v>
       </x:c>
       <x:c r="B750" s="17" t="str">
-        <x:v>Pulsera 3x1 Esclava Bebe Oro Laminado 18K</x:v>
+        <x:v>Pulsera 3x1 Esclava Bebé Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C750" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo 3x1 esclava bebé, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D750" s="22" t="n">
         <x:v>91000</x:v>
@@ -29600,7 +29794,9 @@
       <x:c r="F750" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G750" s="16"/>
+      <x:c r="G750" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H750" s="16"/>
       <x:c r="I750" s="24" t="n">
         <x:v>10</x:v>
@@ -29822,10 +30018,10 @@
         <x:v>RR1422</x:v>
       </x:c>
       <x:c r="B756" s="17" t="str">
-        <x:v>Pulsera Escalera Eclava Oro Laminado 18K</x:v>
+        <x:v>Pulsera Escalera Esclava Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C756" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo escalera esclava, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D756" s="22" t="n">
         <x:v>101000</x:v>
@@ -29834,7 +30030,9 @@
       <x:c r="F756" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G756" s="16"/>
+      <x:c r="G756" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H756" s="16"/>
       <x:c r="I756" s="24" t="n">
         <x:v>10</x:v>
@@ -29861,10 +30059,10 @@
         <x:v>RR1405</x:v>
       </x:c>
       <x:c r="B757" s="17" t="str">
-        <x:v>Pulsera Esclava Oro Laminado 18K</x:v>
+        <x:v>Pulsera Esclava Alba Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C757" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo esclava, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D757" s="22" t="n">
         <x:v>147000</x:v>
@@ -29873,7 +30071,9 @@
       <x:c r="F757" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G757" s="16"/>
+      <x:c r="G757" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H757" s="16"/>
       <x:c r="I757" s="24" t="n">
         <x:v>10</x:v>
@@ -29900,10 +30100,10 @@
         <x:v>RR1404</x:v>
       </x:c>
       <x:c r="B758" s="17" t="str">
-        <x:v>Pulsera Esclava Atenea Oro Laminado 18K</x:v>
+        <x:v>Pulsera Esclava Brillo Diario Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C758" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo esclava, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D758" s="22" t="n">
         <x:v>91000</x:v>
@@ -29912,7 +30112,9 @@
       <x:c r="F758" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G758" s="16"/>
+      <x:c r="G758" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H758" s="16"/>
       <x:c r="I758" s="24" t="n">
         <x:v>10</x:v>
@@ -29939,10 +30141,10 @@
         <x:v>RR1392</x:v>
       </x:c>
       <x:c r="B759" s="17" t="str">
-        <x:v>Pulsera Esclava Bebe Oro Laminado 18K</x:v>
+        <x:v>Pulsera Esclava Bebé Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C759" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo esclava bebé, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D759" s="22" t="n">
         <x:v>94500</x:v>
@@ -29951,7 +30153,9 @@
       <x:c r="F759" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G759" s="16"/>
+      <x:c r="G759" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H759" s="16"/>
       <x:c r="I759" s="24" t="n">
         <x:v>10</x:v>
@@ -30020,7 +30224,7 @@
         <x:v>Pulsera Fe Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C761" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo fe, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D761" s="22" t="n">
         <x:v>81000</x:v>
@@ -30029,7 +30233,9 @@
       <x:c r="F761" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G761" s="16"/>
+      <x:c r="G761" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H761" s="16"/>
       <x:c r="I761" s="24" t="n">
         <x:v>10</x:v>
@@ -30098,7 +30304,7 @@
         <x:v>Pulsera Gucci Esclava Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C763" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo gucci esclava, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D763" s="22" t="n">
         <x:v>168000</x:v>
@@ -30107,7 +30313,9 @@
       <x:c r="F763" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G763" s="16"/>
+      <x:c r="G763" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H763" s="16"/>
       <x:c r="I763" s="24" t="n">
         <x:v>10</x:v>
@@ -30137,7 +30345,7 @@
         <x:v>Pulsera Hombre Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C764" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo hombre, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D764" s="22" t="n">
         <x:v>292000</x:v>
@@ -30146,7 +30354,9 @@
       <x:c r="F764" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G764" s="16"/>
+      <x:c r="G764" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H764" s="16"/>
       <x:c r="I764" s="24" t="n">
         <x:v>10</x:v>
@@ -30176,7 +30386,7 @@
         <x:v>Pulsera Hombre Tejido Chino Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C765" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo hombre tejido chino, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D765" s="22" t="n">
         <x:v>175000</x:v>
@@ -30185,7 +30395,9 @@
       <x:c r="F765" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G765" s="16"/>
+      <x:c r="G765" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H765" s="16"/>
       <x:c r="I765" s="24" t="n">
         <x:v>10</x:v>
@@ -30215,7 +30427,7 @@
         <x:v>Pulsera Hombre Tejido Cubana Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C766" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo hombre tejido cubana, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D766" s="22" t="n">
         <x:v>130000</x:v>
@@ -30224,7 +30436,9 @@
       <x:c r="F766" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G766" s="16"/>
+      <x:c r="G766" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H766" s="16"/>
       <x:c r="I766" s="24" t="n">
         <x:v>10</x:v>
@@ -30254,7 +30468,7 @@
         <x:v>Pulsera Tejido Chino Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C767" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo tejido chino, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D767" s="22" t="n">
         <x:v>105000</x:v>
@@ -30263,7 +30477,9 @@
       <x:c r="F767" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G767" s="16"/>
+      <x:c r="G767" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H767" s="16"/>
       <x:c r="I767" s="24" t="n">
         <x:v>10</x:v>
@@ -30293,7 +30509,7 @@
         <x:v>Pulsera Tejido Plana Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C768" s="17" t="str">
-        <x:v>Pulsera en oro laminado 18K, combinable y pensada para sumar brillo sutil a la muñeca. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Pulsera en oro laminado 18K estilo tejido plana, una pieza elegante para complementar el look con brillo sutil. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D768" s="22" t="n">
         <x:v>118000</x:v>
@@ -30302,7 +30518,9 @@
       <x:c r="F768" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G768" s="16"/>
+      <x:c r="G768" s="16" t="str">
+        <x:v>Pulseras</x:v>
+      </x:c>
       <x:c r="H768" s="16"/>
       <x:c r="I768" s="24" t="n">
         <x:v>10</x:v>
@@ -36104,7 +36322,7 @@
         <x:v>Tobillera Tejido Chino Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C917" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Tobillera en oro laminado 18K estilo tejido chino, ideal para sumar un detalle luminoso y femenino. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D917" s="22" t="n">
         <x:v>167000</x:v>
@@ -36113,7 +36331,9 @@
       <x:c r="F917" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G917" s="16"/>
+      <x:c r="G917" s="16" t="str">
+        <x:v>Tobilleras</x:v>
+      </x:c>
       <x:c r="H917" s="16"/>
       <x:c r="I917" s="24" t="n">
         <x:v>10</x:v>
@@ -36140,10 +36360,10 @@
         <x:v>RR0353</x:v>
       </x:c>
       <x:c r="B918" s="17" t="str">
-        <x:v>Topo Balin #4 Oro Laminado 18K</x:v>
+        <x:v>Topos Balín #4 Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C918" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Topos en oro laminado 18K con diseño balín #4, delicados y fáciles de combinar para el día a día. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D918" s="22" t="n">
         <x:v>36000</x:v>
@@ -36152,7 +36372,9 @@
       <x:c r="F918" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G918" s="16"/>
+      <x:c r="G918" s="16" t="str">
+        <x:v>Topos</x:v>
+      </x:c>
       <x:c r="H918" s="16"/>
       <x:c r="I918" s="24" t="n">
         <x:v>10</x:v>
@@ -36179,10 +36401,10 @@
         <x:v>RR0311</x:v>
       </x:c>
       <x:c r="B919" s="17" t="str">
-        <x:v>Topo Circon Redondo Negro Oro Laminado 18K</x:v>
+        <x:v>Topos Circón Redondo Negro Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C919" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Topos en oro laminado 18K con diseño circón redondo negro, delicados y fáciles de combinar para el día a día. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D919" s="22" t="n">
         <x:v>42000</x:v>
@@ -36191,7 +36413,9 @@
       <x:c r="F919" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G919" s="16"/>
+      <x:c r="G919" s="16" t="str">
+        <x:v>Topos</x:v>
+      </x:c>
       <x:c r="H919" s="16"/>
       <x:c r="I919" s="24" t="n">
         <x:v>10</x:v>
@@ -36218,10 +36442,10 @@
         <x:v>RR0028</x:v>
       </x:c>
       <x:c r="B920" s="17" t="str">
-        <x:v>Topo Rayo Oro Laminado 18K</x:v>
+        <x:v>Topos Rayo Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C920" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Topos en oro laminado 18K con diseño rayo, delicados y fáciles de combinar para el día a día. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D920" s="22" t="n">
         <x:v>67000</x:v>
@@ -36230,7 +36454,9 @@
       <x:c r="F920" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G920" s="16"/>
+      <x:c r="G920" s="16" t="str">
+        <x:v>Topos</x:v>
+      </x:c>
       <x:c r="H920" s="16"/>
       <x:c r="I920" s="24" t="n">
         <x:v>10</x:v>
@@ -36257,10 +36483,10 @@
         <x:v>RR0376</x:v>
       </x:c>
       <x:c r="B921" s="17" t="str">
-        <x:v>Topo Smile Oro Laminado 18K</x:v>
+        <x:v>Topos Smile Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C921" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Topos en oro laminado 18K con diseño smile, delicados y fáciles de combinar para el día a día. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D921" s="22" t="n">
         <x:v>39000</x:v>
@@ -36269,7 +36495,9 @@
       <x:c r="F921" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G921" s="16"/>
+      <x:c r="G921" s="16" t="str">
+        <x:v>Topos</x:v>
+      </x:c>
       <x:c r="H921" s="16"/>
       <x:c r="I921" s="24" t="n">
         <x:v>10</x:v>
@@ -36296,10 +36524,10 @@
         <x:v>RR0030</x:v>
       </x:c>
       <x:c r="B922" s="17" t="str">
-        <x:v>Topo Triple Estrellas ⭐ Oro Laminado 18K</x:v>
+        <x:v>Topos Triple Estrellas ⭐ Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C922" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Topos en oro laminado 18K con diseño triple estrellas ⭐, delicados y fáciles de combinar para el día a día. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D922" s="22" t="n">
         <x:v>80000</x:v>
@@ -36308,7 +36536,9 @@
       <x:c r="F922" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G922" s="16"/>
+      <x:c r="G922" s="16" t="str">
+        <x:v>Topos</x:v>
+      </x:c>
       <x:c r="H922" s="16"/>
       <x:c r="I922" s="24" t="n">
         <x:v>10</x:v>
@@ -36338,7 +36568,7 @@
         <x:v>Topos Rolex Oro Laminado 18K</x:v>
       </x:c>
       <x:c r="C923" s="17" t="str">
-        <x:v>Pieza en oro laminado 18K seleccionada para sumar un detalle elegante y fácil de combinar. Consulta disponibilidad por WhatsApp.</x:v>
+        <x:v>Topos en oro laminado 18K con diseño rolex, delicados y fáciles de combinar para el día a día. Consulta disponibilidad por WhatsApp.</x:v>
       </x:c>
       <x:c r="D923" s="22" t="n">
         <x:v>47000</x:v>
@@ -36347,7 +36577,9 @@
       <x:c r="F923" s="16" t="str">
         <x:v>Oro Laminado 18K</x:v>
       </x:c>
-      <x:c r="G923" s="16"/>
+      <x:c r="G923" s="16" t="str">
+        <x:v>Topos</x:v>
+      </x:c>
       <x:c r="H923" s="16"/>
       <x:c r="I923" s="24" t="n">
         <x:v>10</x:v>
